--- a/docs/03_test/部署登録_テストケース.xlsx
+++ b/docs/03_test/部署登録_テストケース.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{10A2970F-4D30-44A3-9691-D0AC5A50F151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49293013-05B9-4211-99F1-B985DA9598FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CEAD7039-9BCC-4AE4-84C0-8CAB20F5C1A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -120,37 +121,22 @@
     <t>手順</t>
   </si>
   <si>
-    <t>期待結果</t>
-  </si>
-  <si>
     <t>判定</t>
   </si>
   <si>
     <t>日付</t>
   </si>
   <si>
-    <t>部署名に空文字を入力し確認ボタンを押す</t>
-  </si>
-  <si>
     <t>「部署名は入力必須です」と表示される</t>
   </si>
   <si>
     <t>〇</t>
   </si>
   <si>
-    <t>Fn+F12を押して開発者ツールを開き、maxlengthの値を21に変更する。その後部署名にaaaaaaaaaaaaaaaaaaaaaを入力する</t>
-  </si>
-  <si>
     <t>「部署名は20文字以内で入力してください」と表示される。</t>
   </si>
   <si>
-    <t>部署名にaaaaaaaaaaaaaaaaaaaaを入力する</t>
-  </si>
-  <si>
     <t>正常に入力できる</t>
-  </si>
-  <si>
-    <t>ホーム画面で部署登録ボタンを押すと入力画面に遷移する</t>
   </si>
   <si>
     <t>入力画面に画面が遷移する</t>
@@ -185,6 +171,26 @@
     <rPh sb="15" eb="17">
       <t>ニュウリョク</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>期待結果(リンクをクリックすることで画面状態を確認できます)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力画面の部署名に空文字を入力し確認ボタンを押す</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力画面の部署名にaaaaaaaaaaaaaaaaaaaaを入力する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ホーム画面で部署登録ボタンを押すと入力画面に遷移する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力画面でFn+F12を押して開発者ツールを開き、maxlengthの値を21に変更する。その後部署名にaaaaaaaaaaaaaaaaaaaaaを入力する</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -763,7 +769,7 @@
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="6" customWidth="1"/>
-    <col min="3" max="3" width="48.75" customWidth="1"/>
+    <col min="3" max="3" width="58.25" customWidth="1"/>
     <col min="4" max="4" width="52.1640625" customWidth="1"/>
     <col min="6" max="6" width="8.5" customWidth="1"/>
   </cols>
@@ -777,13 +783,13 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="24.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
@@ -791,30 +797,30 @@
         <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>5</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>7</v>
       </c>
       <c r="F3" s="5">
         <v>46164</v>
       </c>
     </row>
-    <row r="4" spans="2:6" ht="55" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="2:6" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B4" s="3">
         <v>2</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" s="5">
         <v>46164</v>
@@ -825,13 +831,13 @@
         <v>3</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F5" s="5">
         <v>46164</v>
@@ -842,13 +848,13 @@
         <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" s="5">
         <v>46164</v>
@@ -859,13 +865,13 @@
         <v>5</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F7" s="5">
         <v>46164</v>
@@ -876,13 +882,13 @@
         <v>6</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F8" s="5">
         <v>46164</v>
@@ -893,13 +899,13 @@
         <v>7</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F9" s="5">
         <v>46164</v>
@@ -910,13 +916,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F10" s="5">
         <v>46164</v>
@@ -927,13 +933,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F11" s="5">
         <v>46164</v>
@@ -956,6 +962,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A94F852-FE9C-4D4E-A2D7-5ED7DBB28CCB}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC334B1A-86B4-476A-BF97-6B14877D1534}">
   <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>

--- a/docs/03_test/部署登録_テストケース.xlsx
+++ b/docs/03_test/部署登録_テストケース.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49293013-05B9-4211-99F1-B985DA9598FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB9EE11-B68E-4949-B6AE-3B930A6F6953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CEAD7039-9BCC-4AE4-84C0-8CAB20F5C1A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +44,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="6">
+  <futureMetadata name="XLRICHVALUE" count="7">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -88,8 +87,15 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="6"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="6">
+  <valueMetadata count="7">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -107,13 +113,16 @@
     </bk>
     <bk>
       <rc t="1" v="5"/>
+    </bk>
+    <bk>
+      <rc t="1" v="6"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
   <si>
     <t>No</t>
   </si>
@@ -145,26 +154,44 @@
     <t>確認画面に画面が遷移する</t>
   </si>
   <si>
-    <t>確認画面で登録ボタンを押すと完了画面に遷移する</t>
-  </si>
-  <si>
     <t>完了画面に画面が遷移する</t>
   </si>
   <si>
-    <t>確認画面で戻るボタンを押すと入力画面に戻る</t>
-  </si>
-  <si>
-    <t>完了画面で続けて登録ボタンを押すと入力画面に遷移する</t>
-  </si>
-  <si>
-    <t>完了画面でメニューに戻るボタンを押すとホーム画面に遷移する</t>
-  </si>
-  <si>
     <t>ホーム画面に画面が遷移する</t>
   </si>
   <si>
-    <t>入力画面で部署名　アルバイトと入力し、
-確認ボタンを押すと確認画面に遷移する</t>
+    <t>期待結果(リンクをクリックすることで画面状態を確認できます)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力画面の部署名に空文字を入力し確認ボタンを押す</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力画面の部署名にaaaaaaaaaaaaaaaaaaaaを入力する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力画面でFn+F12を押して開発者ツールを開き、maxlengthの値を21に変更する。その後部署名にaaaaaaaaaaaaaaaaaaaaaを入力する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力画面で部署名　営業部と入力し、確認ボタンを押す</t>
+    <rPh sb="9" eb="12">
+      <t>エイギョウブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ホーム画面で部署登録ボタンを押す</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力画面で部署名　アルバイトと入力し、確認ボタンを押す</t>
     <rPh sb="5" eb="8">
       <t>ブショメイ</t>
     </rPh>
@@ -174,23 +201,44 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>期待結果(リンクをクリックすることで画面状態を確認できます)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>入力画面の部署名に空文字を入力し確認ボタンを押す</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>入力画面の部署名にaaaaaaaaaaaaaaaaaaaaを入力する</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ホーム画面で部署登録ボタンを押すと入力画面に遷移する</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>入力画面でFn+F12を押して開発者ツールを開き、maxlengthの値を21に変更する。その後部署名にaaaaaaaaaaaaaaaaaaaaaを入力する</t>
+    <t>確認画面で登録ボタンを押す</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>確認画面で戻るボタンを押す</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>完了画面で続けて登録ボタンを押す</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>完了画面でメニューに戻るボタンを押す</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「同じ部署名の部署が既に存在しています」と表示される</t>
+    <rPh sb="1" eb="2">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ブショ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ブショ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>スデ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ヒョウジ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -400,7 +448,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -425,6 +473,10 @@
     <v>5</v>
     <v>5</v>
   </rv>
+  <rv s="0">
+    <v>6</v>
+    <v>5</v>
+  </rv>
 </rvData>
 </file>
 
@@ -445,6 +497,7 @@
   <rel r:id="rId4"/>
   <rel r:id="rId5"/>
   <rel r:id="rId6"/>
+  <rel r:id="rId7"/>
 </richValueRels>
 </file>
 
@@ -765,7 +818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AC81865-A474-4CA1-9C9F-F1D2DA7DDBDB}">
-  <dimension ref="B1:F11"/>
+  <dimension ref="B1:F12"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="6" customWidth="1"/>
@@ -783,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>2</v>
@@ -797,7 +850,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>4</v>
@@ -814,7 +867,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>6</v>
@@ -831,7 +884,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>7</v>
@@ -848,7 +901,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>8</v>
@@ -860,32 +913,30 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="6">
+    <row r="7" spans="2:6" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="6"/>
+      <c r="C7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="5">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B8" s="6">
         <v>5</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="7" t="s">
+      <c r="C8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>9</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" s="5">
-        <v>46164</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B8" s="6">
-        <v>6</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>11</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>5</v>
@@ -896,13 +947,13 @@
     </row>
     <row r="9" spans="2:6" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B9" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>5</v>
@@ -913,10 +964,10 @@
     </row>
     <row r="10" spans="2:6" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B10" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>8</v>
@@ -928,20 +979,37 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="11" spans="2:6" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B11" s="6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>5</v>
       </c>
       <c r="F11" s="5">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B12" s="6">
+        <v>9</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="5">
         <v>46164</v>
       </c>
     </row>
@@ -951,29 +1019,20 @@
     <hyperlink ref="D3" location="Sheet2!A1" display="「部署名は入力必須です」と表示される" xr:uid="{EBBA0DF1-7D19-411F-8FAD-621372D7A4CE}"/>
     <hyperlink ref="D4" location="Sheet2!A2" display="「部署名は20文字以内で入力してください」と表示される。" xr:uid="{EACEC415-AEF0-4F64-A4F6-BC2998F1D57B}"/>
     <hyperlink ref="D6" location="Sheet2!A3" display="入力画面に画面が遷移する" xr:uid="{59FB1D14-659D-40EC-87D5-6CA920539995}"/>
-    <hyperlink ref="D7" location="Sheet2!A4" display="確認画面に画面が遷移する" xr:uid="{E9217F18-AA82-42B6-A318-59B84BF24D08}"/>
-    <hyperlink ref="D8" location="Sheet2!A5" display="完了画面に画面が遷移する" xr:uid="{C81E0DBD-9585-428E-9134-EDBF3EDEB7D5}"/>
-    <hyperlink ref="D11" location="Sheet2!A6" display="ホーム画面に画面が遷移する" xr:uid="{CDD1820A-40C8-4A52-ACF2-FF5E61E4AA32}"/>
-    <hyperlink ref="D10" location="Sheet2!A3" display="入力画面に画面が遷移する" xr:uid="{86035B6F-4D51-4CB2-8CB7-200124A3347F}"/>
-    <hyperlink ref="D9" location="Sheet2!A3" display="入力画面に画面が遷移する" xr:uid="{1CCCC41D-3327-48E1-80EE-C93738E24C82}"/>
+    <hyperlink ref="D8" location="Sheet2!A4" display="確認画面に画面が遷移する" xr:uid="{E9217F18-AA82-42B6-A318-59B84BF24D08}"/>
+    <hyperlink ref="D9" location="Sheet2!A5" display="完了画面に画面が遷移する" xr:uid="{C81E0DBD-9585-428E-9134-EDBF3EDEB7D5}"/>
+    <hyperlink ref="D12" location="Sheet2!A6" display="ホーム画面に画面が遷移する" xr:uid="{CDD1820A-40C8-4A52-ACF2-FF5E61E4AA32}"/>
+    <hyperlink ref="D11" location="Sheet2!A3" display="入力画面に画面が遷移する" xr:uid="{86035B6F-4D51-4CB2-8CB7-200124A3347F}"/>
+    <hyperlink ref="D10" location="Sheet2!A3" display="入力画面に画面が遷移する" xr:uid="{1CCCC41D-3327-48E1-80EE-C93738E24C82}"/>
+    <hyperlink ref="D7" location="Sheet2!A7" display="「同じ部署名の部署が既に存在しています」と表示される" xr:uid="{5B9859F9-DCF7-4D97-8CFD-7D4E7AB2C653}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A94F852-FE9C-4D4E-A2D7-5ED7DBB28CCB}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
-  <sheetData/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC334B1A-86B4-476A-BF97-6B14877D1534}">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="42.5" customWidth="1"/>
@@ -1009,6 +1068,11 @@
         <v>#VALUE!</v>
       </c>
     </row>
+    <row r="7" spans="1:1" ht="124.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
